--- a/Excel/TC0001_AksesMenuStudies.xlsx
+++ b/Excel/TC0001_AksesMenuStudies.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\MobileTesting2\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Selenium_Android_CSharp\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B5E5D62-166C-4249-9D24-97778D1E0075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6938A718-3DB6-451A-A677-73570C27053A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2F15E9A0-1C50-4655-9A11-8F4BEDD34A56}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>RUN</t>
   </si>
@@ -57,25 +57,16 @@
     <t>PASSWORD</t>
   </si>
   <si>
-    <t>NAME</t>
-  </si>
-  <si>
     <t>TC0001-01</t>
   </si>
   <si>
-    <t>yusuftriwibowo000@gmail.com</t>
-  </si>
-  <si>
-    <t>Podokoyok1100#</t>
-  </si>
-  <si>
-    <t>Yusuf</t>
-  </si>
-  <si>
     <t>Positif - Pengujian Akses Menu Studies</t>
   </si>
   <si>
     <t>Menguji Fitur Akses Menu Studies - Sukses</t>
+  </si>
+  <si>
+    <t>qwe</t>
   </si>
 </sst>
 </file>
@@ -126,15 +117,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -465,8 +453,8 @@
     <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -489,38 +477,31 @@
       <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>11</v>
-      </c>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{94BC831C-45A7-42CB-900C-7E3B6327FD41}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>